--- a/practice/answers/s1_q12.xlsx
+++ b/practice/answers/s1_q12.xlsx
@@ -526,17 +526,17 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Birch</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>41.2</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Coulee</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -544,17 +544,17 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>44.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Flats</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -566,17 +566,17 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Gully</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.9</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Quarter</t>
+          <t>Hollow</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -661,7 +661,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>COUNT 3, COUNTA 4 -- the difference is the words 'not seeded'. The average is 41.97 over three values. Type 0 into the two blanks and it falls to 25.18, which asserts those fields yielded nothing.</t>
+          <t>COUNT 3, COUNTA 4 -- the difference is the words 'not seeded'. The average is 47.97 over three values. Type 0 into the two blanks and it falls to 28.78, which asserts those fields yielded nothing.</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q12.xlsx
+++ b/practice/answers/s1_q12.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -46,12 +44,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <color rgb="0024302A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="0024302A"/>
       <sz val="10"/>
     </font>
@@ -96,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,20 +105,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -487,26 +479,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Blanks, text, and what the functions count</t>
+          <t>One SUM, three blocks</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>COUNT sees numbers, COUNTA sees anything typed, AVERAGE skips both blanks and text. Filling the blanks with zero would change the claim being made.</t>
+          <t>A range that spans the blank rows happens to give the right answer here. Naming the three ranges says what the total is actually made of.</t>
         </is>
       </c>
     </row>
@@ -514,162 +506,192 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Parcel</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Yield (bu/ac)</t>
+          <t>Acres</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Birch</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>46.9</v>
+          <t>Home quarter</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Coulee</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>52.7</v>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>318</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Flats</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>not seeded</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Gully</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>44.3</v>
-      </c>
-    </row>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Hollow</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
+          <t>River section</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>North strip</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>205</v>
+      </c>
+    </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>COUNT (numbers)</t>
-        </is>
-      </c>
-      <c r="C12" s="8">
-        <f>COUNT(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>COUNTA (anything)</t>
-        </is>
-      </c>
-      <c r="C13" s="8">
-        <f>COUNTA(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D13" s="9">
-        <f>_xlfn.FORMULATEXT(C13)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>South strip</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1"/>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="C14" s="10">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D14" s="9">
-        <f>_xlfn.FORMULATEXT(C14)</f>
-        <v/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>East lease</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="C15" s="11">
-        <f>AVERAGE(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D15" s="9">
-        <f>_xlfn.FORMULATEXT(C15)</f>
-        <v/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Field 1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>SUM / COUNT</t>
-        </is>
-      </c>
-      <c r="C16" s="11">
-        <f>SUM(B5:B10)/COUNT(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>_xlfn.FORMULATEXT(C16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>COUNT 3, COUNTA 4 -- the difference is the words 'not seeded'. The average is 47.97 over three values. Type 0 into the two blanks and it falls to 28.78, which asserts those fields yielded nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Field 2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Field 3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>One range, first to last</t>
+        </is>
+      </c>
+      <c r="C19" s="8">
+        <f>SUM(B6:B17)</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>_xlfn.FORMULATEXT(C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>The three ranges named</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(B6:B8,B11:B12,B15:B17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>_xlfn.FORMULATEXT(C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>...plus a 60-acre rental</t>
+        </is>
+      </c>
+      <c r="C21" s="8">
+        <f>SUM(B6:B8,B11:B12,B15:B17,60)</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>_xlfn.FORMULATEXT(C21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>The first block only</t>
+        </is>
+      </c>
+      <c r="C22" s="8">
+        <f>SUM(B6:B8)</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>_xlfn.FORMULATEXT(C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>1,421 / 1,421 / 1,481 / 556. The first two agree only because nothing unwanted sits between the first acreage and the last. Put a subtotal in one of those blank rows and the single range swallows it without a word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q12.xlsx
+++ b/practice/answers/s1_q12.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,45 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,12 +38,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,26 +74,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,219 +457,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>One SUM, three blocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A range that spans the blank rows happens to give the right answer here. Naming the three ranges says what the total is actually made of.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Parcel</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Acres</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Home quarter</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>NW</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B3" s="2" t="n">
         <v>142</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>SW</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B4" s="2" t="n">
         <v>318</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B5" s="2" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>River section</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>North strip</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B8" s="2" t="n">
         <v>205</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>South strip</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B9" s="2" t="n">
         <v>177</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>East lease</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Field 1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B12" s="2" t="n">
         <v>264</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Field 2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B13" s="2" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Field 3</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B14" s="2" t="n">
         <v>131</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>One range, first to last</t>
-        </is>
-      </c>
-      <c r="C19" s="8">
-        <f>SUM(B6:B17)</f>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Single range</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>SUM(B3:B14)</f>
         <v/>
       </c>
-      <c r="D19" s="9">
-        <f>_xlfn.FORMULATEXT(C19)</f>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Three ranges</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>SUM(B3:B5,B8:B9,B12:B14)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>The three ranges named</t>
-        </is>
-      </c>
-      <c r="C20" s="8">
-        <f>SUM(B6:B8,B11:B12,B15:B17)</f>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>With rented 60 acres</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>SUM(B3:B5,B8:B9,B12:B14,60)</f>
         <v/>
       </c>
-      <c r="D20" s="9">
-        <f>_xlfn.FORMULATEXT(C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>...plus a 60-acre rental</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(B6:B8,B11:B12,B15:B17,60)</f>
-        <v/>
-      </c>
-      <c r="D21" s="9">
-        <f>_xlfn.FORMULATEXT(C21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>The first block only</t>
-        </is>
-      </c>
-      <c r="C22" s="8">
-        <f>SUM(B6:B8)</f>
-        <v/>
-      </c>
-      <c r="D22" s="9">
-        <f>_xlfn.FORMULATEXT(C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>1,421 / 1,421 / 1,481 / 556. The first two agree only because nothing unwanted sits between the first acreage and the last. Put a subtotal in one of those blank rows and the single range swallows it without a word.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>They agree only because everything between the first and last acreage happens to belong in the total. Put a subtotal, a note, or another dataset in one of those blank rows and the single range picks it up without warning; the three named ranges do not.</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>The colleague summed only the Home quarter block: =SUM(B3:B5) = 556 acres, reported as the whole farm. The number is a plausible acreage, no error appears, and nothing on the sheet shows that two-thirds of the land is missing.</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A20:G22"/>
+    <mergeCell ref="A24:G26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
